--- a/Dataset/Hourly Ontario Zonal Price Report.xlsx
+++ b/Dataset/Hourly Ontario Zonal Price Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/678cf581fdec5424/00 - Old Files/Desktop/Courses/BigDataProject/Dataset/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\padwe\OneDrive\00 - Old Files\Documents\GitHub\DataScience_SmartGrid\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{34345E40-B254-4A82-85B4-4077D793565A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EE514EE-5A72-4420-946D-B50786CB5581}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38ABF2BF-F695-4795-8866-38475AD5AB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1D206603-3D3F-4373-8584-B6B5D0ED04A4}"/>
   </bookViews>
@@ -558,8 +558,23 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -576,25 +591,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -611,10 +611,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -942,10 +938,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1298,38 +1294,38 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
     </row>
     <row r="10" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="2">
         <v>1</v>
       </c>
@@ -1640,38 +1636,38 @@
       </c>
     </row>
     <row r="15" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="24"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="29"/>
     </row>
     <row r="16" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="21"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="2">
         <v>1</v>
       </c>
@@ -1982,38 +1978,38 @@
       </c>
     </row>
     <row r="21" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="24"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
+      <c r="V21" s="28"/>
+      <c r="W21" s="28"/>
+      <c r="X21" s="28"/>
+      <c r="Y21" s="29"/>
     </row>
     <row r="22" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="21"/>
+      <c r="A22" s="26"/>
       <c r="B22" s="2">
         <v>1</v>
       </c>
@@ -2324,38 +2320,38 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="24"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="29"/>
     </row>
     <row r="28" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="21"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="2">
         <v>1</v>
       </c>
@@ -2666,38 +2662,38 @@
       </c>
     </row>
     <row r="33" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="23"/>
-      <c r="X33" s="23"/>
-      <c r="Y33" s="24"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
+      <c r="V33" s="28"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="28"/>
+      <c r="Y33" s="29"/>
     </row>
     <row r="34" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="21"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="2">
         <v>1</v>
       </c>
@@ -3008,38 +3004,38 @@
       </c>
     </row>
     <row r="39" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="23"/>
-      <c r="R39" s="23"/>
-      <c r="S39" s="23"/>
-      <c r="T39" s="23"/>
-      <c r="U39" s="23"/>
-      <c r="V39" s="23"/>
-      <c r="W39" s="23"/>
-      <c r="X39" s="23"/>
-      <c r="Y39" s="24"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="29"/>
     </row>
     <row r="40" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="21"/>
+      <c r="A40" s="26"/>
       <c r="B40" s="2">
         <v>1</v>
       </c>
@@ -3350,38 +3346,38 @@
       </c>
     </row>
     <row r="45" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="23"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="23"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="23"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="23"/>
-      <c r="Q45" s="23"/>
-      <c r="R45" s="23"/>
-      <c r="S45" s="23"/>
-      <c r="T45" s="23"/>
-      <c r="U45" s="23"/>
-      <c r="V45" s="23"/>
-      <c r="W45" s="23"/>
-      <c r="X45" s="23"/>
-      <c r="Y45" s="24"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
+      <c r="T45" s="28"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="28"/>
+      <c r="W45" s="28"/>
+      <c r="X45" s="28"/>
+      <c r="Y45" s="29"/>
     </row>
     <row r="46" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="21"/>
+      <c r="A46" s="26"/>
       <c r="B46" s="2">
         <v>1</v>
       </c>
@@ -3692,38 +3688,38 @@
       </c>
     </row>
     <row r="51" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="23"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="23"/>
-      <c r="Q51" s="23"/>
-      <c r="R51" s="23"/>
-      <c r="S51" s="23"/>
-      <c r="T51" s="23"/>
-      <c r="U51" s="23"/>
-      <c r="V51" s="23"/>
-      <c r="W51" s="23"/>
-      <c r="X51" s="23"/>
-      <c r="Y51" s="24"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="28"/>
+      <c r="S51" s="28"/>
+      <c r="T51" s="28"/>
+      <c r="U51" s="28"/>
+      <c r="V51" s="28"/>
+      <c r="W51" s="28"/>
+      <c r="X51" s="28"/>
+      <c r="Y51" s="29"/>
     </row>
     <row r="52" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="21"/>
+      <c r="A52" s="26"/>
       <c r="B52" s="2">
         <v>1</v>
       </c>
@@ -4034,38 +4030,38 @@
       </c>
     </row>
     <row r="57" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="20" t="s">
+      <c r="A57" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="22" t="s">
+      <c r="B57" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="23"/>
-      <c r="J57" s="23"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="23"/>
-      <c r="O57" s="23"/>
-      <c r="P57" s="23"/>
-      <c r="Q57" s="23"/>
-      <c r="R57" s="23"/>
-      <c r="S57" s="23"/>
-      <c r="T57" s="23"/>
-      <c r="U57" s="23"/>
-      <c r="V57" s="23"/>
-      <c r="W57" s="23"/>
-      <c r="X57" s="23"/>
-      <c r="Y57" s="24"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+      <c r="P57" s="28"/>
+      <c r="Q57" s="28"/>
+      <c r="R57" s="28"/>
+      <c r="S57" s="28"/>
+      <c r="T57" s="28"/>
+      <c r="U57" s="28"/>
+      <c r="V57" s="28"/>
+      <c r="W57" s="28"/>
+      <c r="X57" s="28"/>
+      <c r="Y57" s="29"/>
     </row>
     <row r="58" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="21"/>
+      <c r="A58" s="26"/>
       <c r="B58" s="2">
         <v>1</v>
       </c>
@@ -4376,38 +4372,38 @@
       </c>
     </row>
     <row r="63" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="23"/>
-      <c r="J63" s="23"/>
-      <c r="K63" s="23"/>
-      <c r="L63" s="23"/>
-      <c r="M63" s="23"/>
-      <c r="N63" s="23"/>
-      <c r="O63" s="23"/>
-      <c r="P63" s="23"/>
-      <c r="Q63" s="23"/>
-      <c r="R63" s="23"/>
-      <c r="S63" s="23"/>
-      <c r="T63" s="23"/>
-      <c r="U63" s="23"/>
-      <c r="V63" s="23"/>
-      <c r="W63" s="23"/>
-      <c r="X63" s="23"/>
-      <c r="Y63" s="24"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="28"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="M63" s="28"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+      <c r="P63" s="28"/>
+      <c r="Q63" s="28"/>
+      <c r="R63" s="28"/>
+      <c r="S63" s="28"/>
+      <c r="T63" s="28"/>
+      <c r="U63" s="28"/>
+      <c r="V63" s="28"/>
+      <c r="W63" s="28"/>
+      <c r="X63" s="28"/>
+      <c r="Y63" s="29"/>
     </row>
     <row r="64" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="21"/>
+      <c r="A64" s="26"/>
       <c r="B64" s="2">
         <v>1</v>
       </c>
@@ -4718,38 +4714,38 @@
       </c>
     </row>
     <row r="69" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="20" t="s">
+      <c r="A69" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B69" s="22" t="s">
+      <c r="B69" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="23"/>
-      <c r="I69" s="23"/>
-      <c r="J69" s="23"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="23"/>
-      <c r="N69" s="23"/>
-      <c r="O69" s="23"/>
-      <c r="P69" s="23"/>
-      <c r="Q69" s="23"/>
-      <c r="R69" s="23"/>
-      <c r="S69" s="23"/>
-      <c r="T69" s="23"/>
-      <c r="U69" s="23"/>
-      <c r="V69" s="23"/>
-      <c r="W69" s="23"/>
-      <c r="X69" s="23"/>
-      <c r="Y69" s="24"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+      <c r="J69" s="28"/>
+      <c r="K69" s="28"/>
+      <c r="L69" s="28"/>
+      <c r="M69" s="28"/>
+      <c r="N69" s="28"/>
+      <c r="O69" s="28"/>
+      <c r="P69" s="28"/>
+      <c r="Q69" s="28"/>
+      <c r="R69" s="28"/>
+      <c r="S69" s="28"/>
+      <c r="T69" s="28"/>
+      <c r="U69" s="28"/>
+      <c r="V69" s="28"/>
+      <c r="W69" s="28"/>
+      <c r="X69" s="28"/>
+      <c r="Y69" s="29"/>
     </row>
     <row r="70" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="21"/>
+      <c r="A70" s="26"/>
       <c r="B70" s="2">
         <v>1</v>
       </c>
@@ -5060,38 +5056,38 @@
       </c>
     </row>
     <row r="75" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="20" t="s">
+      <c r="A75" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="23"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="23"/>
-      <c r="M75" s="23"/>
-      <c r="N75" s="23"/>
-      <c r="O75" s="23"/>
-      <c r="P75" s="23"/>
-      <c r="Q75" s="23"/>
-      <c r="R75" s="23"/>
-      <c r="S75" s="23"/>
-      <c r="T75" s="23"/>
-      <c r="U75" s="23"/>
-      <c r="V75" s="23"/>
-      <c r="W75" s="23"/>
-      <c r="X75" s="23"/>
-      <c r="Y75" s="24"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="28"/>
+      <c r="J75" s="28"/>
+      <c r="K75" s="28"/>
+      <c r="L75" s="28"/>
+      <c r="M75" s="28"/>
+      <c r="N75" s="28"/>
+      <c r="O75" s="28"/>
+      <c r="P75" s="28"/>
+      <c r="Q75" s="28"/>
+      <c r="R75" s="28"/>
+      <c r="S75" s="28"/>
+      <c r="T75" s="28"/>
+      <c r="U75" s="28"/>
+      <c r="V75" s="28"/>
+      <c r="W75" s="28"/>
+      <c r="X75" s="28"/>
+      <c r="Y75" s="29"/>
     </row>
     <row r="76" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="21"/>
+      <c r="A76" s="26"/>
       <c r="B76" s="2">
         <v>1</v>
       </c>
@@ -5402,38 +5398,38 @@
       </c>
     </row>
     <row r="81" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B81" s="22" t="s">
+      <c r="B81" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C81" s="23"/>
-      <c r="D81" s="23"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="23"/>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="23"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="23"/>
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-      <c r="O81" s="23"/>
-      <c r="P81" s="23"/>
-      <c r="Q81" s="23"/>
-      <c r="R81" s="23"/>
-      <c r="S81" s="23"/>
-      <c r="T81" s="23"/>
-      <c r="U81" s="23"/>
-      <c r="V81" s="23"/>
-      <c r="W81" s="23"/>
-      <c r="X81" s="23"/>
-      <c r="Y81" s="24"/>
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="28"/>
+      <c r="J81" s="28"/>
+      <c r="K81" s="28"/>
+      <c r="L81" s="28"/>
+      <c r="M81" s="28"/>
+      <c r="N81" s="28"/>
+      <c r="O81" s="28"/>
+      <c r="P81" s="28"/>
+      <c r="Q81" s="28"/>
+      <c r="R81" s="28"/>
+      <c r="S81" s="28"/>
+      <c r="T81" s="28"/>
+      <c r="U81" s="28"/>
+      <c r="V81" s="28"/>
+      <c r="W81" s="28"/>
+      <c r="X81" s="28"/>
+      <c r="Y81" s="29"/>
     </row>
     <row r="82" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="21"/>
+      <c r="A82" s="26"/>
       <c r="B82" s="2">
         <v>1</v>
       </c>
@@ -5744,38 +5740,38 @@
       </c>
     </row>
     <row r="87" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="20" t="s">
+      <c r="A87" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B87" s="22" t="s">
+      <c r="B87" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="23"/>
-      <c r="H87" s="23"/>
-      <c r="I87" s="23"/>
-      <c r="J87" s="23"/>
-      <c r="K87" s="23"/>
-      <c r="L87" s="23"/>
-      <c r="M87" s="23"/>
-      <c r="N87" s="23"/>
-      <c r="O87" s="23"/>
-      <c r="P87" s="23"/>
-      <c r="Q87" s="23"/>
-      <c r="R87" s="23"/>
-      <c r="S87" s="23"/>
-      <c r="T87" s="23"/>
-      <c r="U87" s="23"/>
-      <c r="V87" s="23"/>
-      <c r="W87" s="23"/>
-      <c r="X87" s="23"/>
-      <c r="Y87" s="24"/>
+      <c r="C87" s="28"/>
+      <c r="D87" s="28"/>
+      <c r="E87" s="28"/>
+      <c r="F87" s="28"/>
+      <c r="G87" s="28"/>
+      <c r="H87" s="28"/>
+      <c r="I87" s="28"/>
+      <c r="J87" s="28"/>
+      <c r="K87" s="28"/>
+      <c r="L87" s="28"/>
+      <c r="M87" s="28"/>
+      <c r="N87" s="28"/>
+      <c r="O87" s="28"/>
+      <c r="P87" s="28"/>
+      <c r="Q87" s="28"/>
+      <c r="R87" s="28"/>
+      <c r="S87" s="28"/>
+      <c r="T87" s="28"/>
+      <c r="U87" s="28"/>
+      <c r="V87" s="28"/>
+      <c r="W87" s="28"/>
+      <c r="X87" s="28"/>
+      <c r="Y87" s="29"/>
     </row>
     <row r="88" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="21"/>
+      <c r="A88" s="26"/>
       <c r="B88" s="2">
         <v>1</v>
       </c>
@@ -6086,38 +6082,38 @@
       </c>
     </row>
     <row r="93" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="20" t="s">
+      <c r="A93" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B93" s="22" t="s">
+      <c r="B93" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C93" s="23"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="23"/>
-      <c r="K93" s="23"/>
-      <c r="L93" s="23"/>
-      <c r="M93" s="23"/>
-      <c r="N93" s="23"/>
-      <c r="O93" s="23"/>
-      <c r="P93" s="23"/>
-      <c r="Q93" s="23"/>
-      <c r="R93" s="23"/>
-      <c r="S93" s="23"/>
-      <c r="T93" s="23"/>
-      <c r="U93" s="23"/>
-      <c r="V93" s="23"/>
-      <c r="W93" s="23"/>
-      <c r="X93" s="23"/>
-      <c r="Y93" s="24"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="28"/>
+      <c r="J93" s="28"/>
+      <c r="K93" s="28"/>
+      <c r="L93" s="28"/>
+      <c r="M93" s="28"/>
+      <c r="N93" s="28"/>
+      <c r="O93" s="28"/>
+      <c r="P93" s="28"/>
+      <c r="Q93" s="28"/>
+      <c r="R93" s="28"/>
+      <c r="S93" s="28"/>
+      <c r="T93" s="28"/>
+      <c r="U93" s="28"/>
+      <c r="V93" s="28"/>
+      <c r="W93" s="28"/>
+      <c r="X93" s="28"/>
+      <c r="Y93" s="29"/>
     </row>
     <row r="94" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="21"/>
+      <c r="A94" s="26"/>
       <c r="B94" s="2">
         <v>1</v>
       </c>
@@ -6428,38 +6424,38 @@
       </c>
     </row>
     <row r="99" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="20" t="s">
+      <c r="A99" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="22" t="s">
+      <c r="B99" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C99" s="23"/>
-      <c r="D99" s="23"/>
-      <c r="E99" s="23"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="23"/>
-      <c r="H99" s="23"/>
-      <c r="I99" s="23"/>
-      <c r="J99" s="23"/>
-      <c r="K99" s="23"/>
-      <c r="L99" s="23"/>
-      <c r="M99" s="23"/>
-      <c r="N99" s="23"/>
-      <c r="O99" s="23"/>
-      <c r="P99" s="23"/>
-      <c r="Q99" s="23"/>
-      <c r="R99" s="23"/>
-      <c r="S99" s="23"/>
-      <c r="T99" s="23"/>
-      <c r="U99" s="23"/>
-      <c r="V99" s="23"/>
-      <c r="W99" s="23"/>
-      <c r="X99" s="23"/>
-      <c r="Y99" s="24"/>
+      <c r="C99" s="28"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="28"/>
+      <c r="H99" s="28"/>
+      <c r="I99" s="28"/>
+      <c r="J99" s="28"/>
+      <c r="K99" s="28"/>
+      <c r="L99" s="28"/>
+      <c r="M99" s="28"/>
+      <c r="N99" s="28"/>
+      <c r="O99" s="28"/>
+      <c r="P99" s="28"/>
+      <c r="Q99" s="28"/>
+      <c r="R99" s="28"/>
+      <c r="S99" s="28"/>
+      <c r="T99" s="28"/>
+      <c r="U99" s="28"/>
+      <c r="V99" s="28"/>
+      <c r="W99" s="28"/>
+      <c r="X99" s="28"/>
+      <c r="Y99" s="29"/>
     </row>
     <row r="100" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="21"/>
+      <c r="A100" s="26"/>
       <c r="B100" s="2">
         <v>1</v>
       </c>
@@ -6770,38 +6766,38 @@
       </c>
     </row>
     <row r="105" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="20" t="s">
+      <c r="A105" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B105" s="22" t="s">
+      <c r="B105" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C105" s="23"/>
-      <c r="D105" s="23"/>
-      <c r="E105" s="23"/>
-      <c r="F105" s="23"/>
-      <c r="G105" s="23"/>
-      <c r="H105" s="23"/>
-      <c r="I105" s="23"/>
-      <c r="J105" s="23"/>
-      <c r="K105" s="23"/>
-      <c r="L105" s="23"/>
-      <c r="M105" s="23"/>
-      <c r="N105" s="23"/>
-      <c r="O105" s="23"/>
-      <c r="P105" s="23"/>
-      <c r="Q105" s="23"/>
-      <c r="R105" s="23"/>
-      <c r="S105" s="23"/>
-      <c r="T105" s="23"/>
-      <c r="U105" s="23"/>
-      <c r="V105" s="23"/>
-      <c r="W105" s="23"/>
-      <c r="X105" s="23"/>
-      <c r="Y105" s="24"/>
+      <c r="C105" s="28"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="28"/>
+      <c r="F105" s="28"/>
+      <c r="G105" s="28"/>
+      <c r="H105" s="28"/>
+      <c r="I105" s="28"/>
+      <c r="J105" s="28"/>
+      <c r="K105" s="28"/>
+      <c r="L105" s="28"/>
+      <c r="M105" s="28"/>
+      <c r="N105" s="28"/>
+      <c r="O105" s="28"/>
+      <c r="P105" s="28"/>
+      <c r="Q105" s="28"/>
+      <c r="R105" s="28"/>
+      <c r="S105" s="28"/>
+      <c r="T105" s="28"/>
+      <c r="U105" s="28"/>
+      <c r="V105" s="28"/>
+      <c r="W105" s="28"/>
+      <c r="X105" s="28"/>
+      <c r="Y105" s="29"/>
     </row>
     <row r="106" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="21"/>
+      <c r="A106" s="26"/>
       <c r="B106" s="2">
         <v>1</v>
       </c>
@@ -7112,38 +7108,38 @@
       </c>
     </row>
     <row r="111" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="20" t="s">
+      <c r="A111" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B111" s="22" t="s">
+      <c r="B111" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
-      <c r="G111" s="23"/>
-      <c r="H111" s="23"/>
-      <c r="I111" s="23"/>
-      <c r="J111" s="23"/>
-      <c r="K111" s="23"/>
-      <c r="L111" s="23"/>
-      <c r="M111" s="23"/>
-      <c r="N111" s="23"/>
-      <c r="O111" s="23"/>
-      <c r="P111" s="23"/>
-      <c r="Q111" s="23"/>
-      <c r="R111" s="23"/>
-      <c r="S111" s="23"/>
-      <c r="T111" s="23"/>
-      <c r="U111" s="23"/>
-      <c r="V111" s="23"/>
-      <c r="W111" s="23"/>
-      <c r="X111" s="23"/>
-      <c r="Y111" s="24"/>
+      <c r="C111" s="28"/>
+      <c r="D111" s="28"/>
+      <c r="E111" s="28"/>
+      <c r="F111" s="28"/>
+      <c r="G111" s="28"/>
+      <c r="H111" s="28"/>
+      <c r="I111" s="28"/>
+      <c r="J111" s="28"/>
+      <c r="K111" s="28"/>
+      <c r="L111" s="28"/>
+      <c r="M111" s="28"/>
+      <c r="N111" s="28"/>
+      <c r="O111" s="28"/>
+      <c r="P111" s="28"/>
+      <c r="Q111" s="28"/>
+      <c r="R111" s="28"/>
+      <c r="S111" s="28"/>
+      <c r="T111" s="28"/>
+      <c r="U111" s="28"/>
+      <c r="V111" s="28"/>
+      <c r="W111" s="28"/>
+      <c r="X111" s="28"/>
+      <c r="Y111" s="29"/>
     </row>
     <row r="112" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="21"/>
+      <c r="A112" s="26"/>
       <c r="B112" s="2">
         <v>1</v>
       </c>
@@ -7454,38 +7450,38 @@
       </c>
     </row>
     <row r="117" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="20" t="s">
+      <c r="A117" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B117" s="22" t="s">
+      <c r="B117" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C117" s="23"/>
-      <c r="D117" s="23"/>
-      <c r="E117" s="23"/>
-      <c r="F117" s="23"/>
-      <c r="G117" s="23"/>
-      <c r="H117" s="23"/>
-      <c r="I117" s="23"/>
-      <c r="J117" s="23"/>
-      <c r="K117" s="23"/>
-      <c r="L117" s="23"/>
-      <c r="M117" s="23"/>
-      <c r="N117" s="23"/>
-      <c r="O117" s="23"/>
-      <c r="P117" s="23"/>
-      <c r="Q117" s="23"/>
-      <c r="R117" s="23"/>
-      <c r="S117" s="23"/>
-      <c r="T117" s="23"/>
-      <c r="U117" s="23"/>
-      <c r="V117" s="23"/>
-      <c r="W117" s="23"/>
-      <c r="X117" s="23"/>
-      <c r="Y117" s="24"/>
+      <c r="C117" s="28"/>
+      <c r="D117" s="28"/>
+      <c r="E117" s="28"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="28"/>
+      <c r="H117" s="28"/>
+      <c r="I117" s="28"/>
+      <c r="J117" s="28"/>
+      <c r="K117" s="28"/>
+      <c r="L117" s="28"/>
+      <c r="M117" s="28"/>
+      <c r="N117" s="28"/>
+      <c r="O117" s="28"/>
+      <c r="P117" s="28"/>
+      <c r="Q117" s="28"/>
+      <c r="R117" s="28"/>
+      <c r="S117" s="28"/>
+      <c r="T117" s="28"/>
+      <c r="U117" s="28"/>
+      <c r="V117" s="28"/>
+      <c r="W117" s="28"/>
+      <c r="X117" s="28"/>
+      <c r="Y117" s="29"/>
     </row>
     <row r="118" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="21"/>
+      <c r="A118" s="26"/>
       <c r="B118" s="2">
         <v>1</v>
       </c>
@@ -7796,38 +7792,38 @@
       </c>
     </row>
     <row r="123" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="20" t="s">
+      <c r="A123" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B123" s="22" t="s">
+      <c r="B123" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C123" s="23"/>
-      <c r="D123" s="23"/>
-      <c r="E123" s="23"/>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="23"/>
-      <c r="J123" s="23"/>
-      <c r="K123" s="23"/>
-      <c r="L123" s="23"/>
-      <c r="M123" s="23"/>
-      <c r="N123" s="23"/>
-      <c r="O123" s="23"/>
-      <c r="P123" s="23"/>
-      <c r="Q123" s="23"/>
-      <c r="R123" s="23"/>
-      <c r="S123" s="23"/>
-      <c r="T123" s="23"/>
-      <c r="U123" s="23"/>
-      <c r="V123" s="23"/>
-      <c r="W123" s="23"/>
-      <c r="X123" s="23"/>
-      <c r="Y123" s="24"/>
+      <c r="C123" s="28"/>
+      <c r="D123" s="28"/>
+      <c r="E123" s="28"/>
+      <c r="F123" s="28"/>
+      <c r="G123" s="28"/>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28"/>
+      <c r="J123" s="28"/>
+      <c r="K123" s="28"/>
+      <c r="L123" s="28"/>
+      <c r="M123" s="28"/>
+      <c r="N123" s="28"/>
+      <c r="O123" s="28"/>
+      <c r="P123" s="28"/>
+      <c r="Q123" s="28"/>
+      <c r="R123" s="28"/>
+      <c r="S123" s="28"/>
+      <c r="T123" s="28"/>
+      <c r="U123" s="28"/>
+      <c r="V123" s="28"/>
+      <c r="W123" s="28"/>
+      <c r="X123" s="28"/>
+      <c r="Y123" s="29"/>
     </row>
     <row r="124" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="21"/>
+      <c r="A124" s="26"/>
       <c r="B124" s="2">
         <v>1</v>
       </c>
@@ -8138,38 +8134,38 @@
       </c>
     </row>
     <row r="129" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="20" t="s">
+      <c r="A129" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B129" s="22" t="s">
+      <c r="B129" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C129" s="23"/>
-      <c r="D129" s="23"/>
-      <c r="E129" s="23"/>
-      <c r="F129" s="23"/>
-      <c r="G129" s="23"/>
-      <c r="H129" s="23"/>
-      <c r="I129" s="23"/>
-      <c r="J129" s="23"/>
-      <c r="K129" s="23"/>
-      <c r="L129" s="23"/>
-      <c r="M129" s="23"/>
-      <c r="N129" s="23"/>
-      <c r="O129" s="23"/>
-      <c r="P129" s="23"/>
-      <c r="Q129" s="23"/>
-      <c r="R129" s="23"/>
-      <c r="S129" s="23"/>
-      <c r="T129" s="23"/>
-      <c r="U129" s="23"/>
-      <c r="V129" s="23"/>
-      <c r="W129" s="23"/>
-      <c r="X129" s="23"/>
-      <c r="Y129" s="24"/>
+      <c r="C129" s="28"/>
+      <c r="D129" s="28"/>
+      <c r="E129" s="28"/>
+      <c r="F129" s="28"/>
+      <c r="G129" s="28"/>
+      <c r="H129" s="28"/>
+      <c r="I129" s="28"/>
+      <c r="J129" s="28"/>
+      <c r="K129" s="28"/>
+      <c r="L129" s="28"/>
+      <c r="M129" s="28"/>
+      <c r="N129" s="28"/>
+      <c r="O129" s="28"/>
+      <c r="P129" s="28"/>
+      <c r="Q129" s="28"/>
+      <c r="R129" s="28"/>
+      <c r="S129" s="28"/>
+      <c r="T129" s="28"/>
+      <c r="U129" s="28"/>
+      <c r="V129" s="28"/>
+      <c r="W129" s="28"/>
+      <c r="X129" s="28"/>
+      <c r="Y129" s="29"/>
     </row>
     <row r="130" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="21"/>
+      <c r="A130" s="26"/>
       <c r="B130" s="2">
         <v>1</v>
       </c>
@@ -8480,38 +8476,38 @@
       </c>
     </row>
     <row r="135" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="20" t="s">
+      <c r="A135" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B135" s="22" t="s">
+      <c r="B135" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C135" s="23"/>
-      <c r="D135" s="23"/>
-      <c r="E135" s="23"/>
-      <c r="F135" s="23"/>
-      <c r="G135" s="23"/>
-      <c r="H135" s="23"/>
-      <c r="I135" s="23"/>
-      <c r="J135" s="23"/>
-      <c r="K135" s="23"/>
-      <c r="L135" s="23"/>
-      <c r="M135" s="23"/>
-      <c r="N135" s="23"/>
-      <c r="O135" s="23"/>
-      <c r="P135" s="23"/>
-      <c r="Q135" s="23"/>
-      <c r="R135" s="23"/>
-      <c r="S135" s="23"/>
-      <c r="T135" s="23"/>
-      <c r="U135" s="23"/>
-      <c r="V135" s="23"/>
-      <c r="W135" s="23"/>
-      <c r="X135" s="23"/>
-      <c r="Y135" s="24"/>
+      <c r="C135" s="28"/>
+      <c r="D135" s="28"/>
+      <c r="E135" s="28"/>
+      <c r="F135" s="28"/>
+      <c r="G135" s="28"/>
+      <c r="H135" s="28"/>
+      <c r="I135" s="28"/>
+      <c r="J135" s="28"/>
+      <c r="K135" s="28"/>
+      <c r="L135" s="28"/>
+      <c r="M135" s="28"/>
+      <c r="N135" s="28"/>
+      <c r="O135" s="28"/>
+      <c r="P135" s="28"/>
+      <c r="Q135" s="28"/>
+      <c r="R135" s="28"/>
+      <c r="S135" s="28"/>
+      <c r="T135" s="28"/>
+      <c r="U135" s="28"/>
+      <c r="V135" s="28"/>
+      <c r="W135" s="28"/>
+      <c r="X135" s="28"/>
+      <c r="Y135" s="29"/>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="21"/>
+      <c r="A136" s="26"/>
       <c r="B136" s="2">
         <v>1</v>
       </c>
@@ -8822,38 +8818,38 @@
       </c>
     </row>
     <row r="141" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="20" t="s">
+      <c r="A141" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B141" s="22" t="s">
+      <c r="B141" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C141" s="23"/>
-      <c r="D141" s="23"/>
-      <c r="E141" s="23"/>
-      <c r="F141" s="23"/>
-      <c r="G141" s="23"/>
-      <c r="H141" s="23"/>
-      <c r="I141" s="23"/>
-      <c r="J141" s="23"/>
-      <c r="K141" s="23"/>
-      <c r="L141" s="23"/>
-      <c r="M141" s="23"/>
-      <c r="N141" s="23"/>
-      <c r="O141" s="23"/>
-      <c r="P141" s="23"/>
-      <c r="Q141" s="23"/>
-      <c r="R141" s="23"/>
-      <c r="S141" s="23"/>
-      <c r="T141" s="23"/>
-      <c r="U141" s="23"/>
-      <c r="V141" s="23"/>
-      <c r="W141" s="23"/>
-      <c r="X141" s="23"/>
-      <c r="Y141" s="24"/>
+      <c r="C141" s="28"/>
+      <c r="D141" s="28"/>
+      <c r="E141" s="28"/>
+      <c r="F141" s="28"/>
+      <c r="G141" s="28"/>
+      <c r="H141" s="28"/>
+      <c r="I141" s="28"/>
+      <c r="J141" s="28"/>
+      <c r="K141" s="28"/>
+      <c r="L141" s="28"/>
+      <c r="M141" s="28"/>
+      <c r="N141" s="28"/>
+      <c r="O141" s="28"/>
+      <c r="P141" s="28"/>
+      <c r="Q141" s="28"/>
+      <c r="R141" s="28"/>
+      <c r="S141" s="28"/>
+      <c r="T141" s="28"/>
+      <c r="U141" s="28"/>
+      <c r="V141" s="28"/>
+      <c r="W141" s="28"/>
+      <c r="X141" s="28"/>
+      <c r="Y141" s="29"/>
     </row>
     <row r="142" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="21"/>
+      <c r="A142" s="26"/>
       <c r="B142" s="2">
         <v>1</v>
       </c>
@@ -9164,38 +9160,38 @@
       </c>
     </row>
     <row r="147" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="20" t="s">
+      <c r="A147" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B147" s="22" t="s">
+      <c r="B147" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C147" s="23"/>
-      <c r="D147" s="23"/>
-      <c r="E147" s="23"/>
-      <c r="F147" s="23"/>
-      <c r="G147" s="23"/>
-      <c r="H147" s="23"/>
-      <c r="I147" s="23"/>
-      <c r="J147" s="23"/>
-      <c r="K147" s="23"/>
-      <c r="L147" s="23"/>
-      <c r="M147" s="23"/>
-      <c r="N147" s="23"/>
-      <c r="O147" s="23"/>
-      <c r="P147" s="23"/>
-      <c r="Q147" s="23"/>
-      <c r="R147" s="23"/>
-      <c r="S147" s="23"/>
-      <c r="T147" s="23"/>
-      <c r="U147" s="23"/>
-      <c r="V147" s="23"/>
-      <c r="W147" s="23"/>
-      <c r="X147" s="23"/>
-      <c r="Y147" s="24"/>
+      <c r="C147" s="28"/>
+      <c r="D147" s="28"/>
+      <c r="E147" s="28"/>
+      <c r="F147" s="28"/>
+      <c r="G147" s="28"/>
+      <c r="H147" s="28"/>
+      <c r="I147" s="28"/>
+      <c r="J147" s="28"/>
+      <c r="K147" s="28"/>
+      <c r="L147" s="28"/>
+      <c r="M147" s="28"/>
+      <c r="N147" s="28"/>
+      <c r="O147" s="28"/>
+      <c r="P147" s="28"/>
+      <c r="Q147" s="28"/>
+      <c r="R147" s="28"/>
+      <c r="S147" s="28"/>
+      <c r="T147" s="28"/>
+      <c r="U147" s="28"/>
+      <c r="V147" s="28"/>
+      <c r="W147" s="28"/>
+      <c r="X147" s="28"/>
+      <c r="Y147" s="29"/>
     </row>
     <row r="148" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="21"/>
+      <c r="A148" s="26"/>
       <c r="B148" s="2">
         <v>1</v>
       </c>
@@ -9506,38 +9502,38 @@
       </c>
     </row>
     <row r="153" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="20" t="s">
+      <c r="A153" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B153" s="22" t="s">
+      <c r="B153" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C153" s="23"/>
-      <c r="D153" s="23"/>
-      <c r="E153" s="23"/>
-      <c r="F153" s="23"/>
-      <c r="G153" s="23"/>
-      <c r="H153" s="23"/>
-      <c r="I153" s="23"/>
-      <c r="J153" s="23"/>
-      <c r="K153" s="23"/>
-      <c r="L153" s="23"/>
-      <c r="M153" s="23"/>
-      <c r="N153" s="23"/>
-      <c r="O153" s="23"/>
-      <c r="P153" s="23"/>
-      <c r="Q153" s="23"/>
-      <c r="R153" s="23"/>
-      <c r="S153" s="23"/>
-      <c r="T153" s="23"/>
-      <c r="U153" s="23"/>
-      <c r="V153" s="23"/>
-      <c r="W153" s="23"/>
-      <c r="X153" s="23"/>
-      <c r="Y153" s="24"/>
+      <c r="C153" s="28"/>
+      <c r="D153" s="28"/>
+      <c r="E153" s="28"/>
+      <c r="F153" s="28"/>
+      <c r="G153" s="28"/>
+      <c r="H153" s="28"/>
+      <c r="I153" s="28"/>
+      <c r="J153" s="28"/>
+      <c r="K153" s="28"/>
+      <c r="L153" s="28"/>
+      <c r="M153" s="28"/>
+      <c r="N153" s="28"/>
+      <c r="O153" s="28"/>
+      <c r="P153" s="28"/>
+      <c r="Q153" s="28"/>
+      <c r="R153" s="28"/>
+      <c r="S153" s="28"/>
+      <c r="T153" s="28"/>
+      <c r="U153" s="28"/>
+      <c r="V153" s="28"/>
+      <c r="W153" s="28"/>
+      <c r="X153" s="28"/>
+      <c r="Y153" s="29"/>
     </row>
     <row r="154" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="21"/>
+      <c r="A154" s="26"/>
       <c r="B154" s="2">
         <v>1</v>
       </c>
@@ -9848,38 +9844,38 @@
       </c>
     </row>
     <row r="159" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="20" t="s">
+      <c r="A159" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B159" s="22" t="s">
+      <c r="B159" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C159" s="23"/>
-      <c r="D159" s="23"/>
-      <c r="E159" s="23"/>
-      <c r="F159" s="23"/>
-      <c r="G159" s="23"/>
-      <c r="H159" s="23"/>
-      <c r="I159" s="23"/>
-      <c r="J159" s="23"/>
-      <c r="K159" s="23"/>
-      <c r="L159" s="23"/>
-      <c r="M159" s="23"/>
-      <c r="N159" s="23"/>
-      <c r="O159" s="23"/>
-      <c r="P159" s="23"/>
-      <c r="Q159" s="23"/>
-      <c r="R159" s="23"/>
-      <c r="S159" s="23"/>
-      <c r="T159" s="23"/>
-      <c r="U159" s="23"/>
-      <c r="V159" s="23"/>
-      <c r="W159" s="23"/>
-      <c r="X159" s="23"/>
-      <c r="Y159" s="24"/>
+      <c r="C159" s="28"/>
+      <c r="D159" s="28"/>
+      <c r="E159" s="28"/>
+      <c r="F159" s="28"/>
+      <c r="G159" s="28"/>
+      <c r="H159" s="28"/>
+      <c r="I159" s="28"/>
+      <c r="J159" s="28"/>
+      <c r="K159" s="28"/>
+      <c r="L159" s="28"/>
+      <c r="M159" s="28"/>
+      <c r="N159" s="28"/>
+      <c r="O159" s="28"/>
+      <c r="P159" s="28"/>
+      <c r="Q159" s="28"/>
+      <c r="R159" s="28"/>
+      <c r="S159" s="28"/>
+      <c r="T159" s="28"/>
+      <c r="U159" s="28"/>
+      <c r="V159" s="28"/>
+      <c r="W159" s="28"/>
+      <c r="X159" s="28"/>
+      <c r="Y159" s="29"/>
     </row>
     <row r="160" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="21"/>
+      <c r="A160" s="26"/>
       <c r="B160" s="2">
         <v>1</v>
       </c>
@@ -10190,38 +10186,38 @@
       </c>
     </row>
     <row r="165" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="20" t="s">
+      <c r="A165" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B165" s="22" t="s">
+      <c r="B165" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C165" s="23"/>
-      <c r="D165" s="23"/>
-      <c r="E165" s="23"/>
-      <c r="F165" s="23"/>
-      <c r="G165" s="23"/>
-      <c r="H165" s="23"/>
-      <c r="I165" s="23"/>
-      <c r="J165" s="23"/>
-      <c r="K165" s="23"/>
-      <c r="L165" s="23"/>
-      <c r="M165" s="23"/>
-      <c r="N165" s="23"/>
-      <c r="O165" s="23"/>
-      <c r="P165" s="23"/>
-      <c r="Q165" s="23"/>
-      <c r="R165" s="23"/>
-      <c r="S165" s="23"/>
-      <c r="T165" s="23"/>
-      <c r="U165" s="23"/>
-      <c r="V165" s="23"/>
-      <c r="W165" s="23"/>
-      <c r="X165" s="23"/>
-      <c r="Y165" s="24"/>
+      <c r="C165" s="28"/>
+      <c r="D165" s="28"/>
+      <c r="E165" s="28"/>
+      <c r="F165" s="28"/>
+      <c r="G165" s="28"/>
+      <c r="H165" s="28"/>
+      <c r="I165" s="28"/>
+      <c r="J165" s="28"/>
+      <c r="K165" s="28"/>
+      <c r="L165" s="28"/>
+      <c r="M165" s="28"/>
+      <c r="N165" s="28"/>
+      <c r="O165" s="28"/>
+      <c r="P165" s="28"/>
+      <c r="Q165" s="28"/>
+      <c r="R165" s="28"/>
+      <c r="S165" s="28"/>
+      <c r="T165" s="28"/>
+      <c r="U165" s="28"/>
+      <c r="V165" s="28"/>
+      <c r="W165" s="28"/>
+      <c r="X165" s="28"/>
+      <c r="Y165" s="29"/>
     </row>
     <row r="166" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="21"/>
+      <c r="A166" s="26"/>
       <c r="B166" s="2">
         <v>1</v>
       </c>
@@ -10532,38 +10528,38 @@
       </c>
     </row>
     <row r="171" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="20" t="s">
+      <c r="A171" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B171" s="22" t="s">
+      <c r="B171" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C171" s="23"/>
-      <c r="D171" s="23"/>
-      <c r="E171" s="23"/>
-      <c r="F171" s="23"/>
-      <c r="G171" s="23"/>
-      <c r="H171" s="23"/>
-      <c r="I171" s="23"/>
-      <c r="J171" s="23"/>
-      <c r="K171" s="23"/>
-      <c r="L171" s="23"/>
-      <c r="M171" s="23"/>
-      <c r="N171" s="23"/>
-      <c r="O171" s="23"/>
-      <c r="P171" s="23"/>
-      <c r="Q171" s="23"/>
-      <c r="R171" s="23"/>
-      <c r="S171" s="23"/>
-      <c r="T171" s="23"/>
-      <c r="U171" s="23"/>
-      <c r="V171" s="23"/>
-      <c r="W171" s="23"/>
-      <c r="X171" s="23"/>
-      <c r="Y171" s="24"/>
+      <c r="C171" s="28"/>
+      <c r="D171" s="28"/>
+      <c r="E171" s="28"/>
+      <c r="F171" s="28"/>
+      <c r="G171" s="28"/>
+      <c r="H171" s="28"/>
+      <c r="I171" s="28"/>
+      <c r="J171" s="28"/>
+      <c r="K171" s="28"/>
+      <c r="L171" s="28"/>
+      <c r="M171" s="28"/>
+      <c r="N171" s="28"/>
+      <c r="O171" s="28"/>
+      <c r="P171" s="28"/>
+      <c r="Q171" s="28"/>
+      <c r="R171" s="28"/>
+      <c r="S171" s="28"/>
+      <c r="T171" s="28"/>
+      <c r="U171" s="28"/>
+      <c r="V171" s="28"/>
+      <c r="W171" s="28"/>
+      <c r="X171" s="28"/>
+      <c r="Y171" s="29"/>
     </row>
     <row r="172" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="21"/>
+      <c r="A172" s="26"/>
       <c r="B172" s="2">
         <v>1</v>
       </c>
@@ -10874,38 +10870,38 @@
       </c>
     </row>
     <row r="177" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="20" t="s">
+      <c r="A177" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B177" s="22" t="s">
+      <c r="B177" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C177" s="23"/>
-      <c r="D177" s="23"/>
-      <c r="E177" s="23"/>
-      <c r="F177" s="23"/>
-      <c r="G177" s="23"/>
-      <c r="H177" s="23"/>
-      <c r="I177" s="23"/>
-      <c r="J177" s="23"/>
-      <c r="K177" s="23"/>
-      <c r="L177" s="23"/>
-      <c r="M177" s="23"/>
-      <c r="N177" s="23"/>
-      <c r="O177" s="23"/>
-      <c r="P177" s="23"/>
-      <c r="Q177" s="23"/>
-      <c r="R177" s="23"/>
-      <c r="S177" s="23"/>
-      <c r="T177" s="23"/>
-      <c r="U177" s="23"/>
-      <c r="V177" s="23"/>
-      <c r="W177" s="23"/>
-      <c r="X177" s="23"/>
-      <c r="Y177" s="24"/>
+      <c r="C177" s="28"/>
+      <c r="D177" s="28"/>
+      <c r="E177" s="28"/>
+      <c r="F177" s="28"/>
+      <c r="G177" s="28"/>
+      <c r="H177" s="28"/>
+      <c r="I177" s="28"/>
+      <c r="J177" s="28"/>
+      <c r="K177" s="28"/>
+      <c r="L177" s="28"/>
+      <c r="M177" s="28"/>
+      <c r="N177" s="28"/>
+      <c r="O177" s="28"/>
+      <c r="P177" s="28"/>
+      <c r="Q177" s="28"/>
+      <c r="R177" s="28"/>
+      <c r="S177" s="28"/>
+      <c r="T177" s="28"/>
+      <c r="U177" s="28"/>
+      <c r="V177" s="28"/>
+      <c r="W177" s="28"/>
+      <c r="X177" s="28"/>
+      <c r="Y177" s="29"/>
     </row>
     <row r="178" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="21"/>
+      <c r="A178" s="26"/>
       <c r="B178" s="2">
         <v>1</v>
       </c>
@@ -11216,38 +11212,38 @@
       </c>
     </row>
     <row r="183" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="20" t="s">
+      <c r="A183" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B183" s="22" t="s">
+      <c r="B183" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C183" s="23"/>
-      <c r="D183" s="23"/>
-      <c r="E183" s="23"/>
-      <c r="F183" s="23"/>
-      <c r="G183" s="23"/>
-      <c r="H183" s="23"/>
-      <c r="I183" s="23"/>
-      <c r="J183" s="23"/>
-      <c r="K183" s="23"/>
-      <c r="L183" s="23"/>
-      <c r="M183" s="23"/>
-      <c r="N183" s="23"/>
-      <c r="O183" s="23"/>
-      <c r="P183" s="23"/>
-      <c r="Q183" s="23"/>
-      <c r="R183" s="23"/>
-      <c r="S183" s="23"/>
-      <c r="T183" s="23"/>
-      <c r="U183" s="23"/>
-      <c r="V183" s="23"/>
-      <c r="W183" s="23"/>
-      <c r="X183" s="23"/>
-      <c r="Y183" s="24"/>
+      <c r="C183" s="28"/>
+      <c r="D183" s="28"/>
+      <c r="E183" s="28"/>
+      <c r="F183" s="28"/>
+      <c r="G183" s="28"/>
+      <c r="H183" s="28"/>
+      <c r="I183" s="28"/>
+      <c r="J183" s="28"/>
+      <c r="K183" s="28"/>
+      <c r="L183" s="28"/>
+      <c r="M183" s="28"/>
+      <c r="N183" s="28"/>
+      <c r="O183" s="28"/>
+      <c r="P183" s="28"/>
+      <c r="Q183" s="28"/>
+      <c r="R183" s="28"/>
+      <c r="S183" s="28"/>
+      <c r="T183" s="28"/>
+      <c r="U183" s="28"/>
+      <c r="V183" s="28"/>
+      <c r="W183" s="28"/>
+      <c r="X183" s="28"/>
+      <c r="Y183" s="29"/>
     </row>
     <row r="184" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="21"/>
+      <c r="A184" s="26"/>
       <c r="B184" s="2">
         <v>1</v>
       </c>
@@ -11558,38 +11554,38 @@
       </c>
     </row>
     <row r="189" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="20" t="s">
+      <c r="A189" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B189" s="22" t="s">
+      <c r="B189" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C189" s="23"/>
-      <c r="D189" s="23"/>
-      <c r="E189" s="23"/>
-      <c r="F189" s="23"/>
-      <c r="G189" s="23"/>
-      <c r="H189" s="23"/>
-      <c r="I189" s="23"/>
-      <c r="J189" s="23"/>
-      <c r="K189" s="23"/>
-      <c r="L189" s="23"/>
-      <c r="M189" s="23"/>
-      <c r="N189" s="23"/>
-      <c r="O189" s="23"/>
-      <c r="P189" s="23"/>
-      <c r="Q189" s="23"/>
-      <c r="R189" s="23"/>
-      <c r="S189" s="23"/>
-      <c r="T189" s="23"/>
-      <c r="U189" s="23"/>
-      <c r="V189" s="23"/>
-      <c r="W189" s="23"/>
-      <c r="X189" s="23"/>
-      <c r="Y189" s="24"/>
+      <c r="C189" s="28"/>
+      <c r="D189" s="28"/>
+      <c r="E189" s="28"/>
+      <c r="F189" s="28"/>
+      <c r="G189" s="28"/>
+      <c r="H189" s="28"/>
+      <c r="I189" s="28"/>
+      <c r="J189" s="28"/>
+      <c r="K189" s="28"/>
+      <c r="L189" s="28"/>
+      <c r="M189" s="28"/>
+      <c r="N189" s="28"/>
+      <c r="O189" s="28"/>
+      <c r="P189" s="28"/>
+      <c r="Q189" s="28"/>
+      <c r="R189" s="28"/>
+      <c r="S189" s="28"/>
+      <c r="T189" s="28"/>
+      <c r="U189" s="28"/>
+      <c r="V189" s="28"/>
+      <c r="W189" s="28"/>
+      <c r="X189" s="28"/>
+      <c r="Y189" s="29"/>
     </row>
     <row r="190" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="21"/>
+      <c r="A190" s="26"/>
       <c r="B190" s="2">
         <v>1</v>
       </c>
@@ -11900,38 +11896,38 @@
       </c>
     </row>
     <row r="195" spans="1:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="20" t="s">
+      <c r="A195" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B195" s="22" t="s">
+      <c r="B195" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C195" s="23"/>
-      <c r="D195" s="23"/>
-      <c r="E195" s="23"/>
-      <c r="F195" s="23"/>
-      <c r="G195" s="23"/>
-      <c r="H195" s="23"/>
-      <c r="I195" s="23"/>
-      <c r="J195" s="23"/>
-      <c r="K195" s="23"/>
-      <c r="L195" s="23"/>
-      <c r="M195" s="23"/>
-      <c r="N195" s="23"/>
-      <c r="O195" s="23"/>
-      <c r="P195" s="23"/>
-      <c r="Q195" s="23"/>
-      <c r="R195" s="23"/>
-      <c r="S195" s="23"/>
-      <c r="T195" s="23"/>
-      <c r="U195" s="23"/>
-      <c r="V195" s="23"/>
-      <c r="W195" s="23"/>
-      <c r="X195" s="23"/>
-      <c r="Y195" s="24"/>
+      <c r="C195" s="28"/>
+      <c r="D195" s="28"/>
+      <c r="E195" s="28"/>
+      <c r="F195" s="28"/>
+      <c r="G195" s="28"/>
+      <c r="H195" s="28"/>
+      <c r="I195" s="28"/>
+      <c r="J195" s="28"/>
+      <c r="K195" s="28"/>
+      <c r="L195" s="28"/>
+      <c r="M195" s="28"/>
+      <c r="N195" s="28"/>
+      <c r="O195" s="28"/>
+      <c r="P195" s="28"/>
+      <c r="Q195" s="28"/>
+      <c r="R195" s="28"/>
+      <c r="S195" s="28"/>
+      <c r="T195" s="28"/>
+      <c r="U195" s="28"/>
+      <c r="V195" s="28"/>
+      <c r="W195" s="28"/>
+      <c r="X195" s="28"/>
+      <c r="Y195" s="29"/>
     </row>
     <row r="196" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="21"/>
+      <c r="A196" s="26"/>
       <c r="B196" s="2">
         <v>1</v>
       </c>
@@ -12238,60 +12234,6 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="B183:Y183"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="B189:Y189"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="B195:Y195"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="B165:Y165"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="B171:Y171"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="B177:Y177"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="B147:Y147"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="B153:Y153"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="B159:Y159"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:Y129"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="B135:Y135"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B141:Y141"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:Y111"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="B117:Y117"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B123:Y123"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:Y93"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:Y99"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="B105:Y105"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:Y75"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:Y81"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:Y87"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:Y57"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:Y63"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:Y69"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:Y39"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:Y45"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:Y51"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:Y27"/>
@@ -12303,6 +12245,60 @@
     <mergeCell ref="B15:Y15"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B21:Y21"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:Y39"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:Y45"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:Y51"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:Y57"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:Y63"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:Y69"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:Y75"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:Y81"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:Y87"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:Y93"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:Y99"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="B105:Y105"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:Y111"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B117:Y117"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B123:Y123"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:Y129"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="B135:Y135"/>
+    <mergeCell ref="A141:A142"/>
+    <mergeCell ref="B141:Y141"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="B147:Y147"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="B153:Y153"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="B159:Y159"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="B165:Y165"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="B171:Y171"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="B177:Y177"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="B183:Y183"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="B189:Y189"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="B195:Y195"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A15" r:id="rId1" display="https://reports-public.ieso.ca/public/DAHourlyOntarioZonalPrice/PUB_DAHourlyOntarioZonalPrice_20250516.xml" xr:uid="{B4D2B064-6D14-499C-BFFF-DDF52C833642}"/>
@@ -12386,43 +12382,43 @@
     <col min="6" max="6" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="31" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:25" s="24" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="28" t="str" cm="1">
+      <c r="C1" s="21" t="str" cm="1">
         <f t="array" ref="C1:E1">TRANSPOSE(Sheet1!A5:A7)</f>
         <v>Zonal Price</v>
       </c>
-      <c r="D1" s="28" t="str">
+      <c r="D1" s="21" t="str">
         <v>Energy Loss Price</v>
       </c>
-      <c r="E1" s="28" t="str">
+      <c r="E1" s="21" t="str">
         <v>Energy Congestion Price</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
